--- a/database/RAIL3.xlsx
+++ b/database/RAIL3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2837"/>
+  <dimension ref="A1:F2838"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57151,20 +57151,32 @@
       <c r="A2837" s="1" t="n">
         <v>46282</v>
       </c>
-      <c r="B2837" t="n">
-        <v>14.94</v>
-      </c>
-      <c r="C2837" t="n">
-        <v>14.98</v>
-      </c>
-      <c r="D2837" t="n">
-        <v>14.61</v>
-      </c>
-      <c r="E2837" t="n">
-        <v>14.98</v>
-      </c>
+      <c r="B2837" t="inlineStr"/>
+      <c r="C2837" t="inlineStr"/>
+      <c r="D2837" t="inlineStr"/>
+      <c r="E2837" t="inlineStr"/>
       <c r="F2837" t="n">
-        <v>8632200</v>
+        <v>14437900</v>
+      </c>
+    </row>
+    <row r="2838">
+      <c r="A2838" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B2838" t="n">
+        <v>14.97</v>
+      </c>
+      <c r="C2838" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="D2838" t="n">
+        <v>14.72</v>
+      </c>
+      <c r="E2838" t="n">
+        <v>14.79</v>
+      </c>
+      <c r="F2838" t="n">
+        <v>15176100</v>
       </c>
     </row>
   </sheetData>
